--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.004175713698370327</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.004175713698370327</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.004175713698370327</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.004175713698370327</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.008220316652351669</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.008087003705889667</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.004043501852944833</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.004043501852944833</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.008087003705889667</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.004043501852944833</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.004043501852944833</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.0039809383911766</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>2</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.007961876782353201</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.0039809383911766</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.0039809383911766</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0039809383911766</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0039809383911766</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.003924228792898591</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.003924228792898591</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.003924228792898591</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>1</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.003924228792898591</v>

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2015-02-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.003080888607145049</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1206,42 +1206,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1303,38 +1303,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2015-02-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1440,42 +1440,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2015-03-01</t>
+          <t>2015-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2015-03</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2015-03-01</t>
+          <t>2015-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2015-03</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
+          <t>2015-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2015-04</t>
+          <t>2015-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004175713698370327</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
+          <t>2015-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2015-04</t>
+          <t>2015-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2323,22 +2323,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2015-05-01</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2015-05</t>
+          <t>2015-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.004175713698370327</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2482,19 +2482,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2015-05-01</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2015-05</t>
+          <t>2015-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
+          <t>2015-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2015-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
+          <t>2015-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2015-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
+          <t>2015-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
+          <t>2015-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3502,22 +3502,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2015-08-01</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.004175713698370327</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3661,19 +3661,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2015-08-01</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2015-09-01</t>
+          <t>2015-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2015-09-01</t>
+          <t>2015-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4288,22 +4288,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2015-10-01</t>
+          <t>2015-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.004175713698370327</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4447,19 +4447,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2015-10-01</t>
+          <t>2015-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2015-10</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2015-11-01</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2015-11-01</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2015-10</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004175713698370327</v>
+        <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5233,19 +5233,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5467,22 +5467,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.004175713698370327</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5626,19 +5626,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2016-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2016-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6253,22 +6253,22 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.003072817060581456</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -6315,42 +6315,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6412,38 +6412,38 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -6503,17 +6503,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -6549,42 +6549,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2016-05-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2016-05-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2016-05</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-05</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8218,22 +8218,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2016-08-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.008220316652351669</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8377,19 +8377,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2016-08-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2016-09</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9004,22 +9004,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.008220316652351669</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9163,19 +9163,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2016-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10969,22 +10969,22 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.008087003705889667</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -11128,19 +11128,19 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11362,22 +11362,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R56" t="n">
-        <v>0.004043501852944833</v>
+        <v>0.01072225475660665</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11386,12 +11386,12 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -11424,42 +11424,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11491,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11521,38 +11521,38 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2017-04</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11658,42 +11658,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11755,12 +11755,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12148,22 +12148,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2017-06-01</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>0.004043501852944833</v>
+        <v>0.008087003705889667</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12307,19 +12307,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2017-06-01</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12541,22 +12541,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.004043501852944833</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12700,19 +12700,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12934,22 +12934,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2017-08-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.008087003705889667</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13093,19 +13093,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2017-08-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13327,22 +13327,22 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.004043501852944833</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13486,19 +13486,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2017-09</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14113,22 +14113,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2017-11-01</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004043501852944833</v>
+        <v>0.008087003705889667</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14272,19 +14272,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2017-11-01</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004043501852944833</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14665,19 +14665,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2017-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15292,22 +15292,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.004043501852944833</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15451,19 +15451,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15685,22 +15685,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2018-03-01</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.004043501852944833</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15844,19 +15844,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2018-03-01</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16078,12 +16078,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2018-04-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2018-04-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16441,12 +16441,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -16471,22 +16471,22 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0039809383911766</v>
+        <v>0.007631310917654835</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16495,12 +16495,12 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -16533,42 +16533,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16600,12 +16600,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -16630,38 +16630,38 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -16671,12 +16671,12 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG83" t="inlineStr">
@@ -16721,17 +16721,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -16767,42 +16767,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16864,12 +16864,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -17023,12 +17023,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17257,22 +17257,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.007961876782353201</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17416,19 +17416,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17650,22 +17650,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0039809383911766</v>
+        <v>0</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17809,19 +17809,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18436,22 +18436,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0039809383911766</v>
+        <v>0</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18595,19 +18595,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18829,22 +18829,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0039809383911766</v>
+        <v>0.007961876782353201</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18988,19 +18988,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19222,22 +19222,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.0039809383911766</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19381,19 +19381,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19615,22 +19615,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.0039809383911766</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19774,19 +19774,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20008,22 +20008,22 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.0039809383911766</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20167,19 +20167,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -20416,7 +20416,7 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0.003924228792898591</v>
+        <v>0.0039809383911766</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20560,12 +20560,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -20953,12 +20953,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21187,12 +21187,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -21346,12 +21346,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21550,12 +21550,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21580,22 +21580,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.003042775690577341</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21604,12 +21604,12 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -21642,42 +21642,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21709,12 +21709,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21739,38 +21739,38 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Syphilis congenital</t>
+          <t>Syphilis, congenital</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
@@ -21830,17 +21830,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital syphilis notifications.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+          <t>SER_FR_ECDC_CONSYPH_ANNUAL</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -21876,42 +21876,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21973,22 +21973,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.003924228792898591</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -22132,19 +22132,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22366,22 +22366,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>0.003924228792898591</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22525,19 +22525,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22759,22 +22759,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.003924228792898591</v>
+        <v>0</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22918,19 +22918,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23152,12 +23152,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -23311,12 +23311,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23545,12 +23545,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -23704,12 +23704,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23938,12 +23938,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24268,6 +24268,1971 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.003924228792898591</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.003924228792898591</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>congenital-syphilis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D167</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Congenital syphilis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>先天性梅毒</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Syphilis congenital</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital syphilis notifications.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -24389,7 +26354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -24399,7 +26364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24419,7 +26384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -24429,7 +26394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24451,7 +26416,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
